--- a/artfynd/A 37456-2023 artfynd.xlsx
+++ b/artfynd/A 37456-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37456-2023 artfynd.xlsx
+++ b/artfynd/A 37456-2023 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>111717027</v>
       </c>
       <c r="B2" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -712,14 +707,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fastarby (Fastarby), Upl</t>
+          <t>Fastarby, Fastarby, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>692412</v>
       </c>
       <c r="R2" t="n">
-        <v>6610353</v>
+        <v>6610354</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -788,54 +783,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111717478</v>
+        <v>111726607</v>
       </c>
       <c r="B3" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fastarby (Fastarby), Upl</t>
+          <t>Fastarby Gård, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692412</v>
+        <v>692418</v>
       </c>
       <c r="R3" t="n">
-        <v>6610353</v>
+        <v>6610341</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,19 +854,9 @@
           <t>2023-08-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +865,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,41 +888,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111726607</v>
+        <v>111726400</v>
       </c>
       <c r="B4" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>5741</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -948,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692418</v>
+        <v>692355</v>
       </c>
       <c r="R4" t="n">
-        <v>6610340</v>
+        <v>6610646</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1015,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111726400</v>
+        <v>111717478</v>
       </c>
       <c r="B5" t="n">
-        <v>88934</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,48 +1012,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5741</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fastarby Gård, Upl</t>
+          <t>Fastarby, Fastarby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692355</v>
+        <v>692412</v>
       </c>
       <c r="R5" t="n">
-        <v>6610646</v>
+        <v>6610354</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,9 +1070,19 @@
           <t>2023-08-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,7 +1091,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
